--- a/data/trans_camb/P3A_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,54</t>
+          <t>-0,51; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,54</t>
+          <t>0,86; 8,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,49</t>
+          <t>-4,04; 3,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,62</t>
+          <t>-1,68; 2,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,27</t>
+          <t>-1,37; 3,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,76</t>
+          <t>-0,44; 3,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,39</t>
+          <t>-0,4; 3,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,58</t>
+          <t>0,02; 4,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,67</t>
+          <t>-1,6; 2,6</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 43,86</t>
+          <t>-2,94; 43,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 54,55</t>
+          <t>4,33; 54,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 22,08</t>
+          <t>-21,61; 25,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 43,03</t>
+          <t>-19,7; 37,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 51,41</t>
+          <t>-16,91; 52,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 59,16</t>
+          <t>-5,49; 58,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 32,15</t>
+          <t>-3,22; 31,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 42,27</t>
+          <t>-0,21; 40,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 24,54</t>
+          <t>-12,97; 23,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,43</t>
+          <t>4,39; 10,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,65</t>
+          <t>9,78; 15,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 9,18</t>
+          <t>-4,68; 9,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,23</t>
+          <t>2,47; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,48</t>
+          <t>5,77; 10,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,41</t>
+          <t>3,62; 12,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,39</t>
+          <t>4,44; 8,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,45</t>
+          <t>8,6; 12,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,02</t>
+          <t>2,01; 9,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 54,1</t>
+          <t>19,07; 53,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,84; 81,8</t>
+          <t>42,78; 79,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 45,1</t>
+          <t>-20,53; 45,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 68,91</t>
+          <t>19,1; 69,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,49; 99,3</t>
+          <t>44,79; 101,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,81; 112,27</t>
+          <t>30,83; 116,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,26; 53,11</t>
+          <t>25,46; 53,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,62; 78,09</t>
+          <t>48,94; 79,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 62,39</t>
+          <t>12,71; 60,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,67</t>
+          <t>3,1; 15,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 20,77</t>
+          <t>8,55; 20,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,57</t>
+          <t>4,91; 15,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,09</t>
+          <t>-3,56; 8,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,16</t>
+          <t>1,4; 12,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 11,64</t>
+          <t>0,97; 10,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,45</t>
+          <t>1,63; 10,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,88</t>
+          <t>6,66; 15,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,79</t>
+          <t>3,92; 11,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 63,8</t>
+          <t>9,37; 62,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,96; 83,8</t>
+          <t>27,3; 82,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,11; 63,6</t>
+          <t>16,01; 64,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 41,31</t>
+          <t>-12,72; 37,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 55,01</t>
+          <t>4,93; 56,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 55,15</t>
+          <t>2,8; 48,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 42,35</t>
+          <t>5,68; 42,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,78; 61,17</t>
+          <t>23,96; 64,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,16; 48,66</t>
+          <t>14,14; 49,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,73</t>
+          <t>4,54; 8,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 13,77</t>
+          <t>9,29; 13,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,03</t>
+          <t>-1,42; 8,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,54</t>
+          <t>1,12; 4,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,45</t>
+          <t>4,83; 8,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,16</t>
+          <t>4,03; 10,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,05</t>
+          <t>3,28; 6,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,27</t>
+          <t>7,65; 10,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,09</t>
+          <t>4,08; 8,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,36; 43,78</t>
+          <t>21,02; 45,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,4; 69,88</t>
+          <t>42,37; 68,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 44,47</t>
+          <t>-5,98; 44,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,67; 41,05</t>
+          <t>8,51; 41,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,14; 76,07</t>
+          <t>37,47; 75,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,56; 89,92</t>
+          <t>35,08; 89,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,86; 38,27</t>
+          <t>19,29; 38,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,66; 65,93</t>
+          <t>44,86; 66,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,46; 57,69</t>
+          <t>25,06; 55,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,82</t>
+          <t>-0,6; 6,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,41</t>
+          <t>0,87; 8,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,83</t>
+          <t>-3,67; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,45</t>
+          <t>-1,54; 2,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,38</t>
+          <t>-1,33; 3,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,71</t>
+          <t>-0,75; 3,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,39</t>
+          <t>-0,46; 3,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,44</t>
+          <t>0,11; 4,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,6</t>
+          <t>-1,53; 2,51</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>-1,07%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 43,44</t>
+          <t>-3,89; 41,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 54,6</t>
+          <t>4,45; 53,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 25,12</t>
+          <t>-19,69; 22,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 37,42</t>
+          <t>-18,9; 39,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 52,74</t>
+          <t>-15,94; 46,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 58,62</t>
+          <t>-9,13; 53,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 31,7</t>
+          <t>-4,06; 31,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 40,62</t>
+          <t>0,48; 40,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 23,99</t>
+          <t>-12,45; 23,26</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>9,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,56</t>
+          <t>4,78; 10,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,59</t>
+          <t>10,0; 15,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 9,12</t>
+          <t>5,09; 11,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,45</t>
+          <t>2,37; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,52</t>
+          <t>5,81; 10,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,56</t>
+          <t>8,87; 13,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,45</t>
+          <t>4,41; 8,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 12,38</t>
+          <t>8,56; 12,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,73</t>
+          <t>7,69; 11,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 53,95</t>
+          <t>20,87; 53,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,78; 79,77</t>
+          <t>43,65; 81,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 45,43</t>
+          <t>22,4; 56,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 69,87</t>
+          <t>17,99; 66,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,79; 101,12</t>
+          <t>43,95; 98,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,83; 116,01</t>
+          <t>67,64; 129,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,46; 53,58</t>
+          <t>25,09; 53,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,94; 79,21</t>
+          <t>48,49; 79,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 60,64</t>
+          <t>43,77; 73,02</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,36</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 15,66</t>
+          <t>3,06; 14,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 20,34</t>
+          <t>8,46; 20,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 15,68</t>
+          <t>5,36; 16,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 8,68</t>
+          <t>-3,11; 9,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,69</t>
+          <t>1,48; 12,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,87</t>
+          <t>-0,07; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,46</t>
+          <t>1,81; 10,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 15,13</t>
+          <t>6,63; 14,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,74</t>
+          <t>3,98; 11,28</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 62,43</t>
+          <t>10,22; 60,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,3; 82,21</t>
+          <t>27,29; 80,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 64,5</t>
+          <t>17,46; 65,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 37,82</t>
+          <t>-10,64; 43,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,93; 56,55</t>
+          <t>5,06; 55,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 48,74</t>
+          <t>0,0; 47,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 42,88</t>
+          <t>6,2; 43,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,96; 64,01</t>
+          <t>23,03; 60,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 49,05</t>
+          <t>13,8; 47,25</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>8,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,68</t>
+          <t>4,51; 8,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,69</t>
+          <t>9,27; 13,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,96</t>
+          <t>5,96; 10,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,6</t>
+          <t>1,26; 4,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,3</t>
+          <t>4,98; 8,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,15</t>
+          <t>7,86; 10,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,1</t>
+          <t>3,27; 6,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,52</t>
+          <t>7,52; 10,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,84</t>
+          <t>7,42; 10,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,02; 45,14</t>
+          <t>20,63; 44,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,37; 68,87</t>
+          <t>42,3; 68,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 44,1</t>
+          <t>27,44; 52,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 41,28</t>
+          <t>9,96; 41,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,47; 75,02</t>
+          <t>38,77; 75,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,08; 89,79</t>
+          <t>60,32; 97,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,29; 38,56</t>
+          <t>19,48; 39,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,86; 66,8</t>
+          <t>44,62; 67,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,06; 55,89</t>
+          <t>42,88; 63,71</t>
         </is>
       </c>
     </row>
